--- a/backend/data/financials_by_company/1ADE.MI.xlsx
+++ b/backend/data/financials_by_company/1ADE.MI.xlsx
@@ -672,58 +672,58 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>283908.382329</v>
+        <v>44744.116138</v>
       </c>
       <c r="C2" t="n">
-        <v>0.319237</v>
+        <v>0.321752</v>
       </c>
       <c r="D2" t="n">
-        <v>2027311.74</v>
+        <v>19762150.98</v>
       </c>
       <c r="E2" t="n">
-        <v>889333.52</v>
+        <v>139064.05</v>
       </c>
       <c r="F2" t="n">
-        <v>889333.52</v>
+        <v>139064.05</v>
       </c>
       <c r="G2" t="n">
-        <v>1793050.47</v>
+        <v>13373717.36</v>
       </c>
       <c r="H2" t="n">
-        <v>251808.76</v>
+        <v>145637.52</v>
       </c>
       <c r="I2" t="n">
-        <v>3124424.02</v>
+        <v>2934325.46</v>
       </c>
       <c r="J2" t="n">
-        <v>2916645.26</v>
+        <v>19901215.03</v>
       </c>
       <c r="K2" t="n">
-        <v>2664836.5</v>
+        <v>19755577.51</v>
       </c>
       <c r="L2" t="n">
-        <v>50888.55</v>
+        <v>-24676.02</v>
       </c>
       <c r="M2" t="n">
-        <v>30952</v>
+        <v>37547.36</v>
       </c>
       <c r="N2" t="n">
-        <v>81840.55</v>
+        <v>12871.34</v>
       </c>
       <c r="O2" t="n">
-        <v>1187625.332329</v>
+        <v>13279397.426138</v>
       </c>
       <c r="P2" t="n">
-        <v>1793050.47</v>
+        <v>13373717.36</v>
       </c>
       <c r="Q2" t="n">
-        <v>7626383.66</v>
+        <v>5796441.35</v>
       </c>
       <c r="R2" t="n">
-        <v>49838.53</v>
+        <v>39613.18</v>
       </c>
       <c r="S2" t="n">
         <v>5000000</v>
@@ -732,148 +732,148 @@
         <v>5000000</v>
       </c>
       <c r="U2" t="n">
-        <v>0.36</v>
+        <v>2.67</v>
       </c>
       <c r="V2" t="n">
-        <v>0.36</v>
+        <v>2.67</v>
       </c>
       <c r="W2" t="n">
-        <v>1793050.47</v>
+        <v>13373717.36</v>
       </c>
       <c r="X2" t="n">
-        <v>1793050.47</v>
+        <v>13373717.36</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>1793050.47</v>
+        <v>13373717.36</v>
       </c>
       <c r="AA2" t="n">
-        <v>1793050.47</v>
+        <v>13373717.36</v>
       </c>
       <c r="AB2" t="n">
-        <v>1793050.47</v>
+        <v>13373717.36</v>
       </c>
       <c r="AC2" t="n">
-        <v>840834.03</v>
+        <v>6344312.79</v>
       </c>
       <c r="AD2" t="n">
-        <v>2633884.5</v>
+        <v>19718030.15</v>
       </c>
       <c r="AE2" t="n">
-        <v>889333.52</v>
+        <v>139064.05</v>
       </c>
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="n">
-        <v>155947.49</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>-1045281.01</v>
+        <v>-139064.05</v>
       </c>
       <c r="AI2" t="n">
-        <v>50888.55</v>
+        <v>-24676.02</v>
       </c>
       <c r="AJ2" t="n">
-        <v>30952</v>
+        <v>37547.36</v>
       </c>
       <c r="AK2" t="n">
-        <v>81840.55</v>
+        <v>12871.34</v>
       </c>
       <c r="AL2" t="n">
-        <v>1745737.44</v>
+        <v>19595722.72</v>
       </c>
       <c r="AM2" t="n">
-        <v>4501959.64</v>
+        <v>2862115.89</v>
       </c>
       <c r="AN2" t="n">
-        <v>2317124.47</v>
+        <v>1427408.91</v>
       </c>
       <c r="AO2" t="n">
-        <v>251808.76</v>
+        <v>145637.52</v>
       </c>
       <c r="AP2" t="n">
-        <v>251808.76</v>
+        <v>145637.52</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1696057.45</v>
+        <v>1360331.28</v>
       </c>
       <c r="AR2" t="n">
-        <v>257997.45</v>
+        <v>688431.1899999999</v>
       </c>
       <c r="AS2" t="n">
-        <v>1438060</v>
+        <v>671900.09</v>
       </c>
       <c r="AT2" t="n">
-        <v>49838.53</v>
+        <v>39613.18</v>
       </c>
       <c r="AU2" t="n">
-        <v>6247697.08</v>
+        <v>22457838.61</v>
       </c>
       <c r="AV2" t="n">
-        <v>3124424.02</v>
+        <v>2934325.46</v>
       </c>
       <c r="AW2" t="n">
-        <v>9372121.1</v>
+        <v>25392164.07</v>
       </c>
       <c r="AX2" t="n">
-        <v>9372121.1</v>
+        <v>25392164.07</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>182681.3685</v>
+        <v>-2545.656401</v>
       </c>
       <c r="C3" t="n">
-        <v>0.15</v>
+        <v>0.356535</v>
       </c>
       <c r="D3" t="n">
-        <v>772144.87</v>
+        <v>1462787.98</v>
       </c>
       <c r="E3" t="n">
-        <v>1217875.79</v>
+        <v>-7140</v>
       </c>
       <c r="F3" t="n">
-        <v>1217875.79</v>
+        <v>-7140</v>
       </c>
       <c r="G3" t="n">
-        <v>1936135.11</v>
+        <v>-2409026.86</v>
       </c>
       <c r="H3" t="n">
-        <v>452468.66</v>
+        <v>5126425.86</v>
       </c>
       <c r="I3" t="n">
-        <v>3181723.91</v>
+        <v>4127038.38</v>
       </c>
       <c r="J3" t="n">
-        <v>1990020.66</v>
+        <v>1455647.98</v>
       </c>
       <c r="K3" t="n">
-        <v>1537552</v>
+        <v>-3670777.88</v>
       </c>
       <c r="L3" t="n">
-        <v>112926.54</v>
+        <v>11845.13</v>
       </c>
       <c r="M3" t="n">
-        <v>33715.7</v>
+        <v>73054.38</v>
       </c>
       <c r="N3" t="n">
-        <v>146642.24</v>
+        <v>84899.50999999999</v>
       </c>
       <c r="O3" t="n">
-        <v>900940.6885</v>
+        <v>-2404432.516401</v>
       </c>
       <c r="P3" t="n">
-        <v>1936135.11</v>
+        <v>-2409026.86</v>
       </c>
       <c r="Q3" t="n">
-        <v>7567468.39</v>
+        <v>12106823.31</v>
       </c>
       <c r="R3" t="n">
-        <v>73694.87</v>
+        <v>69911.78</v>
       </c>
       <c r="S3" t="n">
         <v>5000000</v>
@@ -882,150 +882,148 @@
         <v>5000000</v>
       </c>
       <c r="U3" t="n">
-        <v>0.39</v>
+        <v>-0.48</v>
       </c>
       <c r="V3" t="n">
-        <v>0.39</v>
+        <v>-0.48</v>
       </c>
       <c r="W3" t="n">
-        <v>1936135.11</v>
+        <v>-2409026.86</v>
       </c>
       <c r="X3" t="n">
-        <v>1936135.11</v>
+        <v>-2409026.86</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>1936135.11</v>
+        <v>-2409026.86</v>
       </c>
       <c r="AA3" t="n">
-        <v>1936135.11</v>
+        <v>-2409026.86</v>
       </c>
       <c r="AB3" t="n">
-        <v>1936135.11</v>
+        <v>-2409026.86</v>
       </c>
       <c r="AC3" t="n">
-        <v>-432298.81</v>
+        <v>-1334805.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>1503836.3</v>
+        <v>-3743832.26</v>
       </c>
       <c r="AE3" t="n">
-        <v>1217875.79</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>2400000</v>
-      </c>
+        <v>-7140</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="n">
-        <v>14032.36</v>
+        <v>7140</v>
       </c>
       <c r="AH3" t="n">
-        <v>-3631908.15</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>112926.54</v>
+        <v>11845.13</v>
       </c>
       <c r="AJ3" t="n">
-        <v>33715.7</v>
+        <v>73054.38</v>
       </c>
       <c r="AK3" t="n">
-        <v>146642.24</v>
+        <v>84899.50999999999</v>
       </c>
       <c r="AL3" t="n">
-        <v>183525.82</v>
+        <v>-3762893.95</v>
       </c>
       <c r="AM3" t="n">
-        <v>4385744.48</v>
+        <v>7979784.93</v>
       </c>
       <c r="AN3" t="n">
-        <v>2360957.9</v>
+        <v>1293453.53</v>
       </c>
       <c r="AO3" t="n">
-        <v>450822.4</v>
+        <v>5126425.86</v>
       </c>
       <c r="AP3" t="n">
-        <v>450822.4</v>
+        <v>5126425.86</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1437608.37</v>
+        <v>1390715.67</v>
       </c>
       <c r="AR3" t="n">
-        <v>124223.29</v>
+        <v>304081.91</v>
       </c>
       <c r="AS3" t="n">
-        <v>1313385.08</v>
+        <v>1086633.76</v>
       </c>
       <c r="AT3" t="n">
-        <v>73694.87</v>
+        <v>69911.78</v>
       </c>
       <c r="AU3" t="n">
-        <v>4569270.3</v>
+        <v>4216890.98</v>
       </c>
       <c r="AV3" t="n">
-        <v>3181723.91</v>
+        <v>4127038.38</v>
       </c>
       <c r="AW3" t="n">
-        <v>7750994.21</v>
+        <v>8343929.36</v>
       </c>
       <c r="AX3" t="n">
-        <v>7750994.21</v>
+        <v>8343929.36</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-2545.656401</v>
+        <v>182681.3685</v>
       </c>
       <c r="C4" t="n">
-        <v>0.356535</v>
+        <v>0.15</v>
       </c>
       <c r="D4" t="n">
-        <v>1462787.98</v>
+        <v>772144.87</v>
       </c>
       <c r="E4" t="n">
-        <v>-7140</v>
+        <v>1217875.79</v>
       </c>
       <c r="F4" t="n">
-        <v>-7140</v>
+        <v>1217875.79</v>
       </c>
       <c r="G4" t="n">
-        <v>-2409026.86</v>
+        <v>1936135.11</v>
       </c>
       <c r="H4" t="n">
-        <v>5126425.86</v>
+        <v>452468.66</v>
       </c>
       <c r="I4" t="n">
-        <v>4127038.38</v>
+        <v>3181723.91</v>
       </c>
       <c r="J4" t="n">
-        <v>1455647.98</v>
+        <v>1990020.66</v>
       </c>
       <c r="K4" t="n">
-        <v>-3670777.88</v>
+        <v>1537552</v>
       </c>
       <c r="L4" t="n">
-        <v>11845.13</v>
+        <v>112926.54</v>
       </c>
       <c r="M4" t="n">
-        <v>73054.38</v>
+        <v>33715.7</v>
       </c>
       <c r="N4" t="n">
-        <v>84899.50999999999</v>
+        <v>146642.24</v>
       </c>
       <c r="O4" t="n">
-        <v>-2404432.516401</v>
+        <v>900940.6885</v>
       </c>
       <c r="P4" t="n">
-        <v>-2409026.86</v>
+        <v>1936135.11</v>
       </c>
       <c r="Q4" t="n">
-        <v>12106823.31</v>
+        <v>7567468.39</v>
       </c>
       <c r="R4" t="n">
-        <v>69911.78</v>
+        <v>73694.87</v>
       </c>
       <c r="S4" t="n">
         <v>5000000</v>
@@ -1034,148 +1032,150 @@
         <v>5000000</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.48</v>
+        <v>0.39</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.48</v>
+        <v>0.39</v>
       </c>
       <c r="W4" t="n">
-        <v>-2409026.86</v>
+        <v>1936135.11</v>
       </c>
       <c r="X4" t="n">
-        <v>-2409026.86</v>
+        <v>1936135.11</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>-2409026.86</v>
+        <v>1936135.11</v>
       </c>
       <c r="AA4" t="n">
-        <v>-2409026.86</v>
+        <v>1936135.11</v>
       </c>
       <c r="AB4" t="n">
-        <v>-2409026.86</v>
+        <v>1936135.11</v>
       </c>
       <c r="AC4" t="n">
-        <v>-1334805.4</v>
+        <v>-432298.81</v>
       </c>
       <c r="AD4" t="n">
-        <v>-3743832.26</v>
+        <v>1503836.3</v>
       </c>
       <c r="AE4" t="n">
-        <v>-7140</v>
-      </c>
-      <c r="AF4" t="inlineStr"/>
+        <v>1217875.79</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>2400000</v>
+      </c>
       <c r="AG4" t="n">
-        <v>7140</v>
+        <v>14032.36</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>-3631908.15</v>
       </c>
       <c r="AI4" t="n">
-        <v>11845.13</v>
+        <v>112926.54</v>
       </c>
       <c r="AJ4" t="n">
-        <v>73054.38</v>
+        <v>33715.7</v>
       </c>
       <c r="AK4" t="n">
-        <v>84899.50999999999</v>
+        <v>146642.24</v>
       </c>
       <c r="AL4" t="n">
-        <v>-3762893.95</v>
+        <v>183525.82</v>
       </c>
       <c r="AM4" t="n">
-        <v>7979784.93</v>
+        <v>4385744.48</v>
       </c>
       <c r="AN4" t="n">
-        <v>1293453.53</v>
+        <v>2360957.9</v>
       </c>
       <c r="AO4" t="n">
-        <v>5126425.86</v>
+        <v>450822.4</v>
       </c>
       <c r="AP4" t="n">
-        <v>5126425.86</v>
+        <v>450822.4</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1390715.67</v>
+        <v>1437608.37</v>
       </c>
       <c r="AR4" t="n">
-        <v>304081.91</v>
+        <v>124223.29</v>
       </c>
       <c r="AS4" t="n">
-        <v>1086633.76</v>
+        <v>1313385.08</v>
       </c>
       <c r="AT4" t="n">
-        <v>69911.78</v>
+        <v>73694.87</v>
       </c>
       <c r="AU4" t="n">
-        <v>4216890.98</v>
+        <v>4569270.3</v>
       </c>
       <c r="AV4" t="n">
-        <v>4127038.38</v>
+        <v>3181723.91</v>
       </c>
       <c r="AW4" t="n">
-        <v>8343929.36</v>
+        <v>7750994.21</v>
       </c>
       <c r="AX4" t="n">
-        <v>8343929.36</v>
+        <v>7750994.21</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>44744.116138</v>
+        <v>283908.382329</v>
       </c>
       <c r="C5" t="n">
-        <v>0.321752</v>
+        <v>0.319237</v>
       </c>
       <c r="D5" t="n">
-        <v>19762150.98</v>
+        <v>2027311.74</v>
       </c>
       <c r="E5" t="n">
-        <v>139064.05</v>
+        <v>889333.52</v>
       </c>
       <c r="F5" t="n">
-        <v>139064.05</v>
+        <v>889333.52</v>
       </c>
       <c r="G5" t="n">
-        <v>13373717.36</v>
+        <v>1793050.47</v>
       </c>
       <c r="H5" t="n">
-        <v>145637.52</v>
+        <v>251808.76</v>
       </c>
       <c r="I5" t="n">
-        <v>2934325.46</v>
+        <v>3124424.02</v>
       </c>
       <c r="J5" t="n">
-        <v>19901215.03</v>
+        <v>2916645.26</v>
       </c>
       <c r="K5" t="n">
-        <v>19755577.51</v>
+        <v>2664836.5</v>
       </c>
       <c r="L5" t="n">
-        <v>-24676.02</v>
+        <v>50888.55</v>
       </c>
       <c r="M5" t="n">
-        <v>37547.36</v>
+        <v>30952</v>
       </c>
       <c r="N5" t="n">
-        <v>12871.34</v>
+        <v>81840.55</v>
       </c>
       <c r="O5" t="n">
-        <v>13279397.426138</v>
+        <v>1187625.332329</v>
       </c>
       <c r="P5" t="n">
-        <v>13373717.36</v>
+        <v>1793050.47</v>
       </c>
       <c r="Q5" t="n">
-        <v>5796441.35</v>
+        <v>7626383.66</v>
       </c>
       <c r="R5" t="n">
-        <v>39613.18</v>
+        <v>49838.53</v>
       </c>
       <c r="S5" t="n">
         <v>5000000</v>
@@ -1184,92 +1184,92 @@
         <v>5000000</v>
       </c>
       <c r="U5" t="n">
-        <v>2.67</v>
+        <v>0.36</v>
       </c>
       <c r="V5" t="n">
-        <v>2.67</v>
+        <v>0.36</v>
       </c>
       <c r="W5" t="n">
-        <v>13373717.36</v>
+        <v>1793050.47</v>
       </c>
       <c r="X5" t="n">
-        <v>13373717.36</v>
+        <v>1793050.47</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>13373717.36</v>
+        <v>1793050.47</v>
       </c>
       <c r="AA5" t="n">
-        <v>13373717.36</v>
+        <v>1793050.47</v>
       </c>
       <c r="AB5" t="n">
-        <v>13373717.36</v>
+        <v>1793050.47</v>
       </c>
       <c r="AC5" t="n">
-        <v>6344312.79</v>
+        <v>840834.03</v>
       </c>
       <c r="AD5" t="n">
-        <v>19718030.15</v>
+        <v>2633884.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>139064.05</v>
+        <v>889333.52</v>
       </c>
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>155947.49</v>
       </c>
       <c r="AH5" t="n">
-        <v>-139064.05</v>
+        <v>-1045281.01</v>
       </c>
       <c r="AI5" t="n">
-        <v>-24676.02</v>
+        <v>50888.55</v>
       </c>
       <c r="AJ5" t="n">
-        <v>37547.36</v>
+        <v>30952</v>
       </c>
       <c r="AK5" t="n">
-        <v>12871.34</v>
+        <v>81840.55</v>
       </c>
       <c r="AL5" t="n">
-        <v>19595722.72</v>
+        <v>1745737.44</v>
       </c>
       <c r="AM5" t="n">
-        <v>2862115.89</v>
+        <v>4501959.64</v>
       </c>
       <c r="AN5" t="n">
-        <v>1427408.91</v>
+        <v>2317124.47</v>
       </c>
       <c r="AO5" t="n">
-        <v>145637.52</v>
+        <v>251808.76</v>
       </c>
       <c r="AP5" t="n">
-        <v>145637.52</v>
+        <v>251808.76</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1360331.28</v>
+        <v>1696057.45</v>
       </c>
       <c r="AR5" t="n">
-        <v>688431.1899999999</v>
+        <v>257997.45</v>
       </c>
       <c r="AS5" t="n">
-        <v>671900.09</v>
+        <v>1438060</v>
       </c>
       <c r="AT5" t="n">
-        <v>39613.18</v>
+        <v>49838.53</v>
       </c>
       <c r="AU5" t="n">
-        <v>22457838.61</v>
+        <v>6247697.08</v>
       </c>
       <c r="AV5" t="n">
-        <v>2934325.46</v>
+        <v>3124424.02</v>
       </c>
       <c r="AW5" t="n">
-        <v>25392164.07</v>
+        <v>9372121.1</v>
       </c>
       <c r="AX5" t="n">
-        <v>25392164.07</v>
+        <v>9372121.1</v>
       </c>
     </row>
   </sheetData>
@@ -1565,7 +1565,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
         <v>5000000</v>
@@ -1574,37 +1574,37 @@
         <v>5000000</v>
       </c>
       <c r="D2" t="n">
-        <v>454604.65</v>
+        <v>506054.76</v>
       </c>
       <c r="E2" t="n">
-        <v>-92466163.3</v>
+        <v>-34145387.9</v>
       </c>
       <c r="F2" t="n">
-        <v>278197152.45</v>
+        <v>151653375.66</v>
       </c>
       <c r="G2" t="n">
-        <v>10181847.22</v>
+        <v>13959116.68</v>
       </c>
       <c r="H2" t="n">
-        <v>-92466163.3</v>
+        <v>-34145387.9</v>
       </c>
       <c r="I2" t="n">
-        <v>454604.65</v>
+        <v>506054.76</v>
       </c>
       <c r="J2" t="n">
-        <v>278197152.45</v>
+        <v>151653375.66</v>
       </c>
       <c r="K2" t="n">
-        <v>278197152.45</v>
+        <v>151653375.66</v>
       </c>
       <c r="L2" t="n">
-        <v>278197152.45</v>
+        <v>151653375.66</v>
       </c>
       <c r="M2" t="n">
-        <v>278197152.45</v>
+        <v>151653375.66</v>
       </c>
       <c r="N2" t="n">
-        <v>33927592.68</v>
+        <v>146653375.66</v>
       </c>
       <c r="O2" t="n">
         <v>5000000</v>
@@ -1613,123 +1613,119 @@
         <v>5000000</v>
       </c>
       <c r="Q2" t="n">
-        <v>106684323.98</v>
+        <v>56135068.8</v>
       </c>
       <c r="R2" t="n">
-        <v>103324860.19</v>
+        <v>49075368.15</v>
       </c>
       <c r="S2" t="n">
-        <v>102992353.25</v>
+        <v>48645585.48</v>
       </c>
       <c r="T2" t="n">
-        <v>332506.94</v>
+        <v>429782.67</v>
       </c>
       <c r="U2" t="n">
-        <v>332506.94</v>
+        <v>429782.67</v>
       </c>
       <c r="V2" t="n">
-        <v>3359463.79</v>
+        <v>7059700.65</v>
       </c>
       <c r="W2" t="n">
-        <v>353959.32</v>
+        <v>1088006.34</v>
       </c>
       <c r="X2" t="n">
-        <v>122097.71</v>
+        <v>76272.09</v>
       </c>
       <c r="Y2" t="n">
-        <v>122097.71</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>7301.41</v>
-      </c>
+        <v>76272.09</v>
+      </c>
+      <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="n">
-        <v>2796322.67</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>939550</v>
-      </c>
+        <v>5875880.76</v>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="n">
-        <v>1197275.76</v>
+        <v>5743975</v>
       </c>
       <c r="AD2" t="n">
-        <v>659496.91</v>
+        <v>131905.76</v>
       </c>
       <c r="AE2" t="n">
-        <v>384881476.43</v>
+        <v>207788444.46</v>
       </c>
       <c r="AF2" t="n">
-        <v>371340165.42</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>353348.19</v>
-      </c>
+        <v>186769627.13</v>
+      </c>
+      <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="n">
-        <v>4918.34</v>
+        <v>48526.01</v>
       </c>
       <c r="AI2" t="n">
-        <v>189809.22</v>
+        <v>308058.3</v>
       </c>
       <c r="AJ2" t="n">
-        <v>189809.22</v>
+        <v>308058.3</v>
       </c>
       <c r="AK2" t="n">
-        <v>370663315.75</v>
+        <v>185798763.56</v>
       </c>
       <c r="AL2" t="n">
-        <v>366781089.8</v>
+        <v>181916537.61</v>
       </c>
       <c r="AM2" t="n">
         <v>3882225.95</v>
       </c>
       <c r="AN2" t="n">
-        <v>128773.92</v>
+        <v>614279.26</v>
       </c>
       <c r="AO2" t="n">
-        <v>-764725.66</v>
+        <v>-390933.93</v>
       </c>
       <c r="AP2" t="n">
-        <v>893499.58</v>
+        <v>1005213.19</v>
       </c>
       <c r="AQ2" t="n">
-        <v>893499.58</v>
-      </c>
-      <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="inlineStr"/>
+        <v>310170.86</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>695042.33</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>0</v>
+      </c>
       <c r="AT2" t="n">
-        <v>13541311.01</v>
+        <v>21018817.33</v>
       </c>
       <c r="AU2" t="n">
-        <v>10984.84</v>
+        <v>3901.06</v>
       </c>
       <c r="AV2" t="n">
-        <v>415500</v>
+        <v>375500</v>
       </c>
       <c r="AW2" t="inlineStr"/>
       <c r="AX2" t="n">
-        <v>238077.55</v>
+        <v>62625.24</v>
       </c>
       <c r="AY2" t="n">
-        <v>266842.14</v>
+        <v>275213</v>
       </c>
       <c r="AZ2" t="n">
-        <v>33760.3</v>
+        <v>11823.65</v>
       </c>
       <c r="BA2" t="n">
-        <v>12576146.18</v>
+        <v>20289754.38</v>
       </c>
       <c r="BB2" t="n">
-        <v>389445.92</v>
+        <v>13746.08</v>
       </c>
       <c r="BC2" t="n">
-        <v>12186700.26</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>12186700.26</v>
-      </c>
+        <v>20276008.3</v>
+      </c>
+      <c r="BD2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
         <v>5000000</v>
@@ -1738,37 +1734,37 @@
         <v>5000000</v>
       </c>
       <c r="D3" t="n">
-        <v>401354.93</v>
+        <v>429782.68</v>
       </c>
       <c r="E3" t="n">
-        <v>-31614286.62</v>
+        <v>-2141162.12</v>
       </c>
       <c r="F3" t="n">
-        <v>137913385.12</v>
+        <v>73349958.66</v>
       </c>
       <c r="G3" t="n">
-        <v>11456116.93</v>
+        <v>13692541.96</v>
       </c>
       <c r="H3" t="n">
-        <v>-31614286.62</v>
+        <v>-2141162.12</v>
       </c>
       <c r="I3" t="n">
-        <v>401354.93</v>
+        <v>429782.68</v>
       </c>
       <c r="J3" t="n">
-        <v>137913385.12</v>
+        <v>73349958.66</v>
       </c>
       <c r="K3" t="n">
-        <v>137913385.12</v>
+        <v>73349958.66</v>
       </c>
       <c r="L3" t="n">
-        <v>137913385.12</v>
+        <v>73349958.66</v>
       </c>
       <c r="M3" t="n">
-        <v>137913385.12</v>
+        <v>73349958.66</v>
       </c>
       <c r="N3" t="n">
-        <v>32634542.21</v>
+        <v>31188407.1</v>
       </c>
       <c r="O3" t="n">
         <v>5000000</v>
@@ -1777,121 +1773,127 @@
         <v>5000000</v>
       </c>
       <c r="Q3" t="n">
-        <v>46654215.86</v>
+        <v>21623062</v>
       </c>
       <c r="R3" t="n">
-        <v>43736182.29</v>
+        <v>16710047.91</v>
       </c>
       <c r="S3" t="n">
-        <v>43425014.89</v>
+        <v>16352888.58</v>
       </c>
       <c r="T3" t="n">
-        <v>311167.4</v>
+        <v>357159.33</v>
       </c>
       <c r="U3" t="n">
-        <v>311167.4</v>
+        <v>357159.33</v>
       </c>
       <c r="V3" t="n">
-        <v>2918033.57</v>
+        <v>4913014.09</v>
       </c>
       <c r="W3" t="n">
-        <v>904030.12</v>
+        <v>684753.91</v>
       </c>
       <c r="X3" t="n">
-        <v>90187.53</v>
+        <v>72623.35000000001</v>
       </c>
       <c r="Y3" t="n">
-        <v>90187.53</v>
+        <v>72623.35000000001</v>
       </c>
       <c r="Z3" t="n">
-        <v>4982.04</v>
+        <v>7341.43</v>
       </c>
       <c r="AA3" t="n">
-        <v>1802853.59</v>
+        <v>3360228.14</v>
       </c>
       <c r="AB3" t="n">
-        <v>598080.83</v>
+        <v>277650</v>
       </c>
       <c r="AC3" t="n">
-        <v>795900</v>
+        <v>2803587</v>
       </c>
       <c r="AD3" t="n">
-        <v>408872.76</v>
+        <v>278991.14</v>
       </c>
       <c r="AE3" t="n">
-        <v>184567600.98</v>
+        <v>94973020.66</v>
       </c>
       <c r="AF3" t="n">
-        <v>170193450.48</v>
+        <v>76367464.61</v>
       </c>
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="n">
-        <v>4679.81</v>
+        <v>91029.39999999999</v>
       </c>
       <c r="AI3" t="n">
-        <v>189809.22</v>
+        <v>285764.03</v>
       </c>
       <c r="AJ3" t="n">
-        <v>189809.22</v>
+        <v>285764.03</v>
       </c>
       <c r="AK3" t="n">
-        <v>169527671.74</v>
+        <v>75491120.78</v>
       </c>
       <c r="AL3" t="n">
-        <v>165645445.79</v>
+        <v>71608894.83</v>
       </c>
       <c r="AM3" t="n">
         <v>3882225.95</v>
       </c>
       <c r="AN3" t="n">
-        <v>471289.71</v>
+        <v>499550.4</v>
       </c>
       <c r="AO3" t="n">
-        <v>-628960.09</v>
+        <v>-509333.2</v>
       </c>
       <c r="AP3" t="n">
-        <v>1100249.8</v>
+        <v>1008883.6</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1100249.8</v>
-      </c>
-      <c r="AR3" t="inlineStr"/>
-      <c r="AS3" t="inlineStr"/>
+        <v>1008883.6</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>695042.33</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>0</v>
+      </c>
       <c r="AT3" t="n">
-        <v>14374150.5</v>
+        <v>18605556.05</v>
       </c>
       <c r="AU3" t="n">
-        <v>273851.42</v>
+        <v>2589.95</v>
       </c>
       <c r="AV3" t="n">
-        <v>379500</v>
+        <v>377500</v>
       </c>
       <c r="AW3" t="n">
-        <v>3208000</v>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+        <v>3200000</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>72026.88</v>
+      </c>
       <c r="AY3" t="n">
-        <v>2519320</v>
+        <v>2886779.63</v>
       </c>
       <c r="AZ3" t="n">
-        <v>111514.86</v>
+        <v>62194.51</v>
       </c>
       <c r="BA3" t="n">
-        <v>11089964.22</v>
+        <v>12004465.08</v>
       </c>
       <c r="BB3" t="n">
-        <v>32717.66</v>
+        <v>321465.08</v>
       </c>
       <c r="BC3" t="n">
-        <v>11057246.56</v>
+        <v>11683000</v>
       </c>
       <c r="BD3" t="n">
-        <v>11057246.56</v>
+        <v>11683000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
         <v>5000000</v>
@@ -1900,37 +1902,37 @@
         <v>5000000</v>
       </c>
       <c r="D4" t="n">
-        <v>429782.68</v>
+        <v>401354.93</v>
       </c>
       <c r="E4" t="n">
-        <v>-2141162.12</v>
+        <v>-31614286.62</v>
       </c>
       <c r="F4" t="n">
-        <v>73349958.66</v>
+        <v>137913385.12</v>
       </c>
       <c r="G4" t="n">
-        <v>13692541.96</v>
+        <v>11456116.93</v>
       </c>
       <c r="H4" t="n">
-        <v>-2141162.12</v>
+        <v>-31614286.62</v>
       </c>
       <c r="I4" t="n">
-        <v>429782.68</v>
+        <v>401354.93</v>
       </c>
       <c r="J4" t="n">
-        <v>73349958.66</v>
+        <v>137913385.12</v>
       </c>
       <c r="K4" t="n">
-        <v>73349958.66</v>
+        <v>137913385.12</v>
       </c>
       <c r="L4" t="n">
-        <v>73349958.66</v>
+        <v>137913385.12</v>
       </c>
       <c r="M4" t="n">
-        <v>73349958.66</v>
+        <v>137913385.12</v>
       </c>
       <c r="N4" t="n">
-        <v>31188407.1</v>
+        <v>32634542.21</v>
       </c>
       <c r="O4" t="n">
         <v>5000000</v>
@@ -1939,127 +1941,121 @@
         <v>5000000</v>
       </c>
       <c r="Q4" t="n">
-        <v>21623062</v>
+        <v>46654215.86</v>
       </c>
       <c r="R4" t="n">
-        <v>16710047.91</v>
+        <v>43736182.29</v>
       </c>
       <c r="S4" t="n">
-        <v>16352888.58</v>
+        <v>43425014.89</v>
       </c>
       <c r="T4" t="n">
-        <v>357159.33</v>
+        <v>311167.4</v>
       </c>
       <c r="U4" t="n">
-        <v>357159.33</v>
+        <v>311167.4</v>
       </c>
       <c r="V4" t="n">
-        <v>4913014.09</v>
+        <v>2918033.57</v>
       </c>
       <c r="W4" t="n">
-        <v>684753.91</v>
+        <v>904030.12</v>
       </c>
       <c r="X4" t="n">
-        <v>72623.35000000001</v>
+        <v>90187.53</v>
       </c>
       <c r="Y4" t="n">
-        <v>72623.35000000001</v>
+        <v>90187.53</v>
       </c>
       <c r="Z4" t="n">
-        <v>7341.43</v>
+        <v>4982.04</v>
       </c>
       <c r="AA4" t="n">
-        <v>3360228.14</v>
+        <v>1802853.59</v>
       </c>
       <c r="AB4" t="n">
-        <v>277650</v>
+        <v>598080.83</v>
       </c>
       <c r="AC4" t="n">
-        <v>2803587</v>
+        <v>795900</v>
       </c>
       <c r="AD4" t="n">
-        <v>278991.14</v>
+        <v>408872.76</v>
       </c>
       <c r="AE4" t="n">
-        <v>94973020.66</v>
+        <v>184567600.98</v>
       </c>
       <c r="AF4" t="n">
-        <v>76367464.61</v>
+        <v>170193450.48</v>
       </c>
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="n">
-        <v>91029.39999999999</v>
+        <v>4679.81</v>
       </c>
       <c r="AI4" t="n">
-        <v>285764.03</v>
+        <v>189809.22</v>
       </c>
       <c r="AJ4" t="n">
-        <v>285764.03</v>
+        <v>189809.22</v>
       </c>
       <c r="AK4" t="n">
-        <v>75491120.78</v>
+        <v>169527671.74</v>
       </c>
       <c r="AL4" t="n">
-        <v>71608894.83</v>
+        <v>165645445.79</v>
       </c>
       <c r="AM4" t="n">
         <v>3882225.95</v>
       </c>
       <c r="AN4" t="n">
-        <v>499550.4</v>
+        <v>471289.71</v>
       </c>
       <c r="AO4" t="n">
-        <v>-509333.2</v>
+        <v>-628960.09</v>
       </c>
       <c r="AP4" t="n">
-        <v>1008883.6</v>
+        <v>1100249.8</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1008883.6</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>695042.33</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>0</v>
-      </c>
+        <v>1100249.8</v>
+      </c>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
-        <v>18605556.05</v>
+        <v>14374150.5</v>
       </c>
       <c r="AU4" t="n">
-        <v>2589.95</v>
+        <v>273851.42</v>
       </c>
       <c r="AV4" t="n">
-        <v>377500</v>
+        <v>379500</v>
       </c>
       <c r="AW4" t="n">
-        <v>3200000</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>72026.88</v>
-      </c>
+        <v>3208000</v>
+      </c>
+      <c r="AX4" t="inlineStr"/>
       <c r="AY4" t="n">
-        <v>2886779.63</v>
+        <v>2519320</v>
       </c>
       <c r="AZ4" t="n">
-        <v>62194.51</v>
+        <v>111514.86</v>
       </c>
       <c r="BA4" t="n">
-        <v>12004465.08</v>
+        <v>11089964.22</v>
       </c>
       <c r="BB4" t="n">
-        <v>321465.08</v>
+        <v>32717.66</v>
       </c>
       <c r="BC4" t="n">
-        <v>11683000</v>
+        <v>11057246.56</v>
       </c>
       <c r="BD4" t="n">
-        <v>11683000</v>
+        <v>11057246.56</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
         <v>5000000</v>
@@ -2068,37 +2064,37 @@
         <v>5000000</v>
       </c>
       <c r="D5" t="n">
-        <v>506054.76</v>
+        <v>454604.65</v>
       </c>
       <c r="E5" t="n">
-        <v>-34145387.9</v>
+        <v>-92466163.3</v>
       </c>
       <c r="F5" t="n">
-        <v>151653375.66</v>
+        <v>278197152.45</v>
       </c>
       <c r="G5" t="n">
-        <v>13959116.68</v>
+        <v>10181847.22</v>
       </c>
       <c r="H5" t="n">
-        <v>-34145387.9</v>
+        <v>-92466163.3</v>
       </c>
       <c r="I5" t="n">
-        <v>506054.76</v>
+        <v>454604.65</v>
       </c>
       <c r="J5" t="n">
-        <v>151653375.66</v>
+        <v>278197152.45</v>
       </c>
       <c r="K5" t="n">
-        <v>151653375.66</v>
+        <v>278197152.45</v>
       </c>
       <c r="L5" t="n">
-        <v>151653375.66</v>
+        <v>278197152.45</v>
       </c>
       <c r="M5" t="n">
-        <v>151653375.66</v>
+        <v>278197152.45</v>
       </c>
       <c r="N5" t="n">
-        <v>146653375.66</v>
+        <v>33927592.68</v>
       </c>
       <c r="O5" t="n">
         <v>5000000</v>
@@ -2107,115 +2103,119 @@
         <v>5000000</v>
       </c>
       <c r="Q5" t="n">
-        <v>56135068.8</v>
+        <v>106684323.98</v>
       </c>
       <c r="R5" t="n">
-        <v>49075368.15</v>
+        <v>103324860.19</v>
       </c>
       <c r="S5" t="n">
-        <v>48645585.48</v>
+        <v>102992353.25</v>
       </c>
       <c r="T5" t="n">
-        <v>429782.67</v>
+        <v>332506.94</v>
       </c>
       <c r="U5" t="n">
-        <v>429782.67</v>
+        <v>332506.94</v>
       </c>
       <c r="V5" t="n">
-        <v>7059700.65</v>
+        <v>3359463.79</v>
       </c>
       <c r="W5" t="n">
-        <v>1088006.34</v>
+        <v>353959.32</v>
       </c>
       <c r="X5" t="n">
-        <v>76272.09</v>
+        <v>122097.71</v>
       </c>
       <c r="Y5" t="n">
-        <v>76272.09</v>
-      </c>
-      <c r="Z5" t="inlineStr"/>
+        <v>122097.71</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>7301.41</v>
+      </c>
       <c r="AA5" t="n">
-        <v>5875880.76</v>
-      </c>
-      <c r="AB5" t="inlineStr"/>
+        <v>2796322.67</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>939550</v>
+      </c>
       <c r="AC5" t="n">
-        <v>5743975</v>
+        <v>1197275.76</v>
       </c>
       <c r="AD5" t="n">
-        <v>131905.76</v>
+        <v>659496.91</v>
       </c>
       <c r="AE5" t="n">
-        <v>207788444.46</v>
+        <v>384881476.43</v>
       </c>
       <c r="AF5" t="n">
-        <v>186769627.13</v>
-      </c>
-      <c r="AG5" t="inlineStr"/>
+        <v>371340165.42</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>353348.19</v>
+      </c>
       <c r="AH5" t="n">
-        <v>48526.01</v>
+        <v>4918.34</v>
       </c>
       <c r="AI5" t="n">
-        <v>308058.3</v>
+        <v>189809.22</v>
       </c>
       <c r="AJ5" t="n">
-        <v>308058.3</v>
+        <v>189809.22</v>
       </c>
       <c r="AK5" t="n">
-        <v>185798763.56</v>
+        <v>370663315.75</v>
       </c>
       <c r="AL5" t="n">
-        <v>181916537.61</v>
+        <v>366781089.8</v>
       </c>
       <c r="AM5" t="n">
         <v>3882225.95</v>
       </c>
       <c r="AN5" t="n">
-        <v>614279.26</v>
+        <v>128773.92</v>
       </c>
       <c r="AO5" t="n">
-        <v>-390933.93</v>
+        <v>-764725.66</v>
       </c>
       <c r="AP5" t="n">
-        <v>1005213.19</v>
+        <v>893499.58</v>
       </c>
       <c r="AQ5" t="n">
-        <v>310170.86</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>695042.33</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>0</v>
-      </c>
+        <v>893499.58</v>
+      </c>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
-        <v>21018817.33</v>
+        <v>13541311.01</v>
       </c>
       <c r="AU5" t="n">
-        <v>3901.06</v>
+        <v>10984.84</v>
       </c>
       <c r="AV5" t="n">
-        <v>375500</v>
+        <v>415500</v>
       </c>
       <c r="AW5" t="inlineStr"/>
       <c r="AX5" t="n">
-        <v>62625.24</v>
+        <v>238077.55</v>
       </c>
       <c r="AY5" t="n">
-        <v>275213</v>
+        <v>266842.14</v>
       </c>
       <c r="AZ5" t="n">
-        <v>11823.65</v>
+        <v>33760.3</v>
       </c>
       <c r="BA5" t="n">
-        <v>20289754.38</v>
+        <v>12576146.18</v>
       </c>
       <c r="BB5" t="n">
-        <v>13746.08</v>
+        <v>389445.92</v>
       </c>
       <c r="BC5" t="n">
-        <v>20276008.3</v>
-      </c>
-      <c r="BD5" t="inlineStr"/>
+        <v>12186700.26</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>12186700.26</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2390,38 +2390,38 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>1787999.7</v>
+        <v>8716354.220000001</v>
       </c>
       <c r="C2" t="n">
-        <v>-11234.52</v>
+        <v>-54858.54</v>
       </c>
       <c r="D2" t="n">
-        <v>12186700.26</v>
+        <v>20276008.3</v>
       </c>
       <c r="E2" t="n">
-        <v>11057246.56</v>
+        <v>12010550.33</v>
       </c>
       <c r="F2" t="n">
-        <v>1129453.7</v>
+        <v>8265457.97</v>
       </c>
       <c r="G2" t="n">
-        <v>-622553</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-500000</v>
-      </c>
+        <v>-80468.32000000001</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
-        <v>-47227.52</v>
-      </c>
-      <c r="J2" t="inlineStr"/>
+        <v>-425286.47</v>
+      </c>
+      <c r="J2" t="n">
+        <v>5072.07</v>
+      </c>
       <c r="K2" t="n">
-        <v>-36000</v>
+        <v>-375500</v>
       </c>
       <c r="L2" t="n">
-        <v>-36000</v>
+        <v>-375500</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -2430,87 +2430,85 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>-11227.52</v>
+        <v>-54858.54</v>
       </c>
       <c r="P2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-11234.52</v>
+        <v>-54858.54</v>
       </c>
       <c r="R2" t="n">
-        <v>1799234.22</v>
+        <v>8771212.76</v>
       </c>
       <c r="S2" t="n">
-        <v>1841768.6</v>
+        <v>-4296020.93</v>
       </c>
       <c r="T2" t="n">
-        <v>81840.55</v>
+        <v>11639.27</v>
       </c>
       <c r="U2" t="n">
-        <v>-30952</v>
+        <v>-37547.36</v>
       </c>
       <c r="V2" t="n">
-        <v>-275237.53</v>
+        <v>693688.34</v>
       </c>
       <c r="W2" t="n">
-        <v>-222479.87</v>
+        <v>176714.07</v>
       </c>
       <c r="X2" t="n">
-        <v>-361136.37</v>
+        <v>338695.56</v>
       </c>
       <c r="Y2" t="n">
-        <v>230624.15</v>
+        <v>33489.33</v>
       </c>
       <c r="Z2" t="n">
-        <v>77754.56</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>3576.03</v>
-      </c>
+        <v>144789.38</v>
+      </c>
+      <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="n">
-        <v>251808.76</v>
+        <v>145637.52</v>
       </c>
       <c r="AC2" t="n">
-        <v>75264.67</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>176544.09</v>
+        <v>145637.52</v>
       </c>
       <c r="AE2" t="n">
-        <v>-2656566.14</v>
+        <v>-7488890.25</v>
       </c>
       <c r="AF2" t="n">
-        <v>2582995.95</v>
+        <v>19742706.17</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-3242020.08</v>
+        <v>-4833195.32</v>
       </c>
       <c r="C3" t="n">
-        <v>-40838.94</v>
+        <v>-20173.31</v>
       </c>
       <c r="D3" t="n">
-        <v>11057246.56</v>
+        <v>14882910.95</v>
       </c>
       <c r="E3" t="n">
-        <v>14882910.95</v>
+        <v>20276008.3</v>
       </c>
       <c r="F3" t="n">
-        <v>-3825664.39</v>
+        <v>-5393097.35</v>
       </c>
       <c r="G3" t="n">
-        <v>-581645.3100000001</v>
+        <v>-576272.08</v>
       </c>
       <c r="H3" t="n">
         <v>-500000</v>
       </c>
       <c r="I3" t="n">
-        <v>-42837.94</v>
+        <v>-3803.26</v>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
@@ -2526,87 +2524,85 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-40837.94</v>
+        <v>-1803.26</v>
       </c>
       <c r="P3" t="n">
-        <v>1</v>
+        <v>18370.05</v>
       </c>
       <c r="Q3" t="n">
-        <v>-40838.94</v>
+        <v>-20173.31</v>
       </c>
       <c r="R3" t="n">
-        <v>-3201181.14</v>
+        <v>-4813022.01</v>
       </c>
       <c r="S3" t="n">
-        <v>-1198333.58</v>
+        <v>-4238155.99</v>
       </c>
       <c r="T3" t="n">
-        <v>146642.24</v>
+        <v>84899.50999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>-33715.7</v>
+        <v>-73054.38</v>
       </c>
       <c r="V3" t="n">
-        <v>92037.06</v>
+        <v>385911.57</v>
       </c>
       <c r="W3" t="n">
-        <v>-158339.32</v>
+        <v>866864.8</v>
       </c>
       <c r="X3" t="n">
-        <v>146215.11</v>
+        <v>-361067.75</v>
       </c>
       <c r="Y3" t="n">
-        <v>153481.62</v>
+        <v>-69514.62</v>
       </c>
       <c r="Z3" t="n">
-        <v>-49320.35</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>73315.2</v>
-      </c>
+        <v>-50370.86</v>
+      </c>
+      <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="n">
-        <v>452468.66</v>
+        <v>5126425.86</v>
       </c>
       <c r="AC3" t="n">
-        <v>330098.77</v>
+        <v>5006325.69</v>
       </c>
       <c r="AD3" t="n">
-        <v>122369.89</v>
+        <v>120100.17</v>
       </c>
       <c r="AE3" t="n">
-        <v>-4124504.78</v>
+        <v>-2343371.19</v>
       </c>
       <c r="AF3" t="n">
-        <v>1390909.76</v>
+        <v>-3755677.39</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-4833195.32</v>
+        <v>-3242020.08</v>
       </c>
       <c r="C4" t="n">
-        <v>-20173.31</v>
+        <v>-40838.94</v>
       </c>
       <c r="D4" t="n">
+        <v>11057246.56</v>
+      </c>
+      <c r="E4" t="n">
         <v>14882910.95</v>
       </c>
-      <c r="E4" t="n">
-        <v>20276008.3</v>
-      </c>
       <c r="F4" t="n">
-        <v>-5393097.35</v>
+        <v>-3825664.39</v>
       </c>
       <c r="G4" t="n">
-        <v>-576272.08</v>
+        <v>-581645.3100000001</v>
       </c>
       <c r="H4" t="n">
         <v>-500000</v>
       </c>
       <c r="I4" t="n">
-        <v>-3803.26</v>
+        <v>-42837.94</v>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
@@ -2622,92 +2618,94 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-1803.26</v>
+        <v>-40837.94</v>
       </c>
       <c r="P4" t="n">
-        <v>18370.05</v>
+        <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>-20173.31</v>
+        <v>-40838.94</v>
       </c>
       <c r="R4" t="n">
-        <v>-4813022.01</v>
+        <v>-3201181.14</v>
       </c>
       <c r="S4" t="n">
-        <v>-4238155.99</v>
+        <v>-1198333.58</v>
       </c>
       <c r="T4" t="n">
-        <v>84899.50999999999</v>
+        <v>146642.24</v>
       </c>
       <c r="U4" t="n">
-        <v>-73054.38</v>
+        <v>-33715.7</v>
       </c>
       <c r="V4" t="n">
-        <v>385911.57</v>
+        <v>92037.06</v>
       </c>
       <c r="W4" t="n">
-        <v>866864.8</v>
+        <v>-158339.32</v>
       </c>
       <c r="X4" t="n">
-        <v>-361067.75</v>
+        <v>146215.11</v>
       </c>
       <c r="Y4" t="n">
-        <v>-69514.62</v>
+        <v>153481.62</v>
       </c>
       <c r="Z4" t="n">
-        <v>-50370.86</v>
-      </c>
-      <c r="AA4" t="inlineStr"/>
+        <v>-49320.35</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>73315.2</v>
+      </c>
       <c r="AB4" t="n">
-        <v>5126425.86</v>
+        <v>452468.66</v>
       </c>
       <c r="AC4" t="n">
-        <v>5006325.69</v>
+        <v>330098.77</v>
       </c>
       <c r="AD4" t="n">
-        <v>120100.17</v>
+        <v>122369.89</v>
       </c>
       <c r="AE4" t="n">
-        <v>-2343371.19</v>
+        <v>-4124504.78</v>
       </c>
       <c r="AF4" t="n">
-        <v>-3755677.39</v>
+        <v>1390909.76</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>8716354.220000001</v>
+        <v>1787999.7</v>
       </c>
       <c r="C5" t="n">
-        <v>-54858.54</v>
+        <v>-11234.52</v>
       </c>
       <c r="D5" t="n">
-        <v>20276008.3</v>
+        <v>12186700.26</v>
       </c>
       <c r="E5" t="n">
-        <v>12010550.33</v>
+        <v>11057246.56</v>
       </c>
       <c r="F5" t="n">
-        <v>8265457.97</v>
+        <v>1129453.7</v>
       </c>
       <c r="G5" t="n">
-        <v>-80468.32000000001</v>
-      </c>
-      <c r="H5" t="inlineStr"/>
+        <v>-622553</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-500000</v>
+      </c>
       <c r="I5" t="n">
-        <v>-425286.47</v>
-      </c>
-      <c r="J5" t="n">
-        <v>5072.07</v>
-      </c>
+        <v>-47227.52</v>
+      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>-375500</v>
+        <v>-36000</v>
       </c>
       <c r="L5" t="n">
-        <v>-375500</v>
+        <v>-36000</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -2716,56 +2714,58 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>-54858.54</v>
+        <v>-11227.52</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q5" t="n">
-        <v>-54858.54</v>
+        <v>-11234.52</v>
       </c>
       <c r="R5" t="n">
-        <v>8771212.76</v>
+        <v>1799234.22</v>
       </c>
       <c r="S5" t="n">
-        <v>-4296020.93</v>
+        <v>1841768.6</v>
       </c>
       <c r="T5" t="n">
-        <v>11639.27</v>
+        <v>81840.55</v>
       </c>
       <c r="U5" t="n">
-        <v>-37547.36</v>
+        <v>-30952</v>
       </c>
       <c r="V5" t="n">
-        <v>693688.34</v>
+        <v>-275237.53</v>
       </c>
       <c r="W5" t="n">
-        <v>176714.07</v>
+        <v>-222479.87</v>
       </c>
       <c r="X5" t="n">
-        <v>338695.56</v>
+        <v>-361136.37</v>
       </c>
       <c r="Y5" t="n">
-        <v>33489.33</v>
+        <v>230624.15</v>
       </c>
       <c r="Z5" t="n">
-        <v>144789.38</v>
-      </c>
-      <c r="AA5" t="inlineStr"/>
+        <v>77754.56</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>3576.03</v>
+      </c>
       <c r="AB5" t="n">
-        <v>145637.52</v>
+        <v>251808.76</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>75264.67</v>
       </c>
       <c r="AD5" t="n">
-        <v>145637.52</v>
+        <v>176544.09</v>
       </c>
       <c r="AE5" t="n">
-        <v>-7488890.25</v>
+        <v>-2656566.14</v>
       </c>
       <c r="AF5" t="n">
-        <v>19742706.17</v>
+        <v>2582995.95</v>
       </c>
     </row>
   </sheetData>
@@ -3290,167 +3290,167 @@
       </c>
       <c r="CX1" t="inlineStr">
         <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="CY1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="CZ1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
           <t>fiftyDayAverageChange</t>
         </is>
       </c>
-      <c r="CY1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="CZ1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChange</t>
         </is>
       </c>
-      <c r="DA1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="DB1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>sourceInterval</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>exchangeDataDelayedBy</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
+      <c r="ED1" t="inlineStr">
         <is>
           <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="DE1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="DF1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
         </is>
       </c>
       <c r="EE1" t="inlineStr">
@@ -3550,34 +3550,34 @@
         <v>2</v>
       </c>
       <c r="T2" t="n">
-        <v>28.42</v>
+        <v>26.64</v>
       </c>
       <c r="U2" t="n">
-        <v>29.4</v>
+        <v>27.8</v>
       </c>
       <c r="V2" t="n">
-        <v>29.4</v>
+        <v>26.3</v>
       </c>
       <c r="W2" t="n">
-        <v>29.4</v>
+        <v>27.8</v>
       </c>
       <c r="X2" t="n">
-        <v>28.42</v>
+        <v>26.64</v>
       </c>
       <c r="Y2" t="n">
-        <v>29.4</v>
+        <v>27.8</v>
       </c>
       <c r="Z2" t="n">
-        <v>29.4</v>
+        <v>26.3</v>
       </c>
       <c r="AA2" t="n">
-        <v>29.4</v>
+        <v>27.8</v>
       </c>
       <c r="AB2" t="n">
         <v>0.1</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.35</v>
+        <v>0.38</v>
       </c>
       <c r="AD2" t="n">
         <v>1756684800</v>
@@ -3586,34 +3586,34 @@
         <v>0.2778</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.781</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="AG2" t="n">
-        <v>35</v>
+        <v>187</v>
       </c>
       <c r="AH2" t="n">
-        <v>35</v>
+        <v>187</v>
       </c>
       <c r="AI2" t="n">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="AJ2" t="n">
-        <v>266</v>
+        <v>356</v>
       </c>
       <c r="AK2" t="n">
-        <v>266</v>
+        <v>356</v>
       </c>
       <c r="AL2" t="n">
-        <v>28</v>
+        <v>26.32</v>
       </c>
       <c r="AM2" t="n">
-        <v>28.86</v>
+        <v>27.2</v>
       </c>
       <c r="AN2" t="n">
-        <v>142200000</v>
+        <v>134000000</v>
       </c>
       <c r="AO2" t="n">
-        <v>142400000</v>
+        <v>131800000</v>
       </c>
       <c r="AP2" t="n">
         <v>25.24</v>
@@ -3628,19 +3628,19 @@
         <v>22.3</v>
       </c>
       <c r="AT2" t="n">
-        <v>15.880823</v>
+        <v>14.965051</v>
       </c>
       <c r="AU2" t="n">
-        <v>30.6584</v>
+        <v>30.13</v>
       </c>
       <c r="AV2" t="n">
-        <v>33.2273</v>
+        <v>32.4268</v>
       </c>
       <c r="AW2" t="n">
         <v>0.1</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.003518649</v>
+        <v>0.0037537538</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
@@ -3651,7 +3651,7 @@
         <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>132931288</v>
+        <v>124731288</v>
       </c>
       <c r="BB2" t="n">
         <v>-0.04449</v>
@@ -3666,7 +3666,7 @@
         <v>0.25</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.034560002</v>
+        <v>0.03376</v>
       </c>
       <c r="BG2" t="n">
         <v>5000000</v>
@@ -3675,7 +3675,7 @@
         <v>53.944</v>
       </c>
       <c r="BI2" t="n">
-        <v>0.5272134000000001</v>
+        <v>0.49681148</v>
       </c>
       <c r="BJ2" t="n">
         <v>1735603200</v>
@@ -3693,16 +3693,16 @@
         <v>-0.08</v>
       </c>
       <c r="BO2" t="n">
-        <v>14.846</v>
+        <v>13.93</v>
       </c>
       <c r="BP2" t="n">
-        <v>107.661</v>
+        <v>101.02</v>
       </c>
       <c r="BQ2" t="n">
-        <v>-0.31682694</v>
+        <v>-0.33499748</v>
       </c>
       <c r="BR2" t="n">
-        <v>0.27449715</v>
+        <v>0.24487448</v>
       </c>
       <c r="BS2" t="n">
         <v>0.1</v>
@@ -3716,7 +3716,7 @@
         </is>
       </c>
       <c r="BV2" t="n">
-        <v>28.44</v>
+        <v>26.8</v>
       </c>
       <c r="BW2" t="inlineStr">
         <is>
@@ -3815,126 +3815,126 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="CX2" t="n">
-        <v>-2.218399</v>
+      <c r="CX2" t="b">
+        <v>0</v>
       </c>
       <c r="CY2" t="n">
-        <v>-0.07235861</v>
+        <v>1701763200000</v>
       </c>
       <c r="CZ2" t="n">
-        <v>-4.787298</v>
+        <v>0.60060006</v>
       </c>
       <c r="DA2" t="n">
-        <v>-0.14407726</v>
-      </c>
-      <c r="DB2" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="DB2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DC2" t="n">
+        <v>1782127133</v>
+      </c>
+      <c r="DD2" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="DE2" t="inlineStr">
+        <is>
+          <t>finmb_241177771</t>
+        </is>
+      </c>
+      <c r="DF2" t="inlineStr">
+        <is>
+          <t>Europe/Rome</t>
+        </is>
+      </c>
+      <c r="DG2" t="inlineStr">
+        <is>
+          <t>CEST</t>
+        </is>
+      </c>
+      <c r="DH2" t="n">
+        <v>7200000</v>
+      </c>
+      <c r="DI2" t="inlineStr">
+        <is>
+          <t>it_market</t>
+        </is>
+      </c>
+      <c r="DJ2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DK2" t="inlineStr">
+        <is>
+          <t>BITCOIN GROUP</t>
+        </is>
+      </c>
+      <c r="DL2" t="inlineStr">
+        <is>
+          <t>PREPRE</t>
+        </is>
+      </c>
+      <c r="DM2" t="n">
+        <v>0.15999985</v>
+      </c>
+      <c r="DN2" t="inlineStr">
+        <is>
+          <t>26.3 - 27.8</t>
+        </is>
+      </c>
+      <c r="DO2" t="inlineStr">
+        <is>
+          <t>Milan</t>
+        </is>
+      </c>
+      <c r="DP2" t="n">
+        <v>417</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>1.5599995</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>0.061806634</v>
+      </c>
+      <c r="DS2" t="inlineStr">
+        <is>
+          <t>25.24 - 49.0</t>
+        </is>
+      </c>
+      <c r="DT2" t="n">
+        <v>-22.2</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>-0.45306125</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>-33.49975</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>-3.33</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>-0.11052108</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>-5.6268005</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>-0.17352316</v>
+      </c>
+      <c r="EB2" t="n">
         <v>20</v>
       </c>
-      <c r="DC2" t="n">
+      <c r="EC2" t="n">
         <v>15</v>
       </c>
-      <c r="DD2" t="b">
+      <c r="ED2" t="b">
         <v>0</v>
-      </c>
-      <c r="DE2" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
-      <c r="DF2" t="inlineStr">
-        <is>
-          <t>finmb_241177771</t>
-        </is>
-      </c>
-      <c r="DG2" t="inlineStr">
-        <is>
-          <t>Europe/Rome</t>
-        </is>
-      </c>
-      <c r="DH2" t="inlineStr">
-        <is>
-          <t>CEST</t>
-        </is>
-      </c>
-      <c r="DI2" t="n">
-        <v>7200000</v>
-      </c>
-      <c r="DJ2" t="inlineStr">
-        <is>
-          <t>it_market</t>
-        </is>
-      </c>
-      <c r="DK2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DL2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="DM2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="DN2" t="n">
-        <v>1780390295</v>
-      </c>
-      <c r="DO2" t="inlineStr">
-        <is>
-          <t>BITCOIN GROUP</t>
-        </is>
-      </c>
-      <c r="DP2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DQ2" t="n">
-        <v>1701763200000</v>
-      </c>
-      <c r="DR2" t="n">
-        <v>0.020000458</v>
-      </c>
-      <c r="DS2" t="inlineStr">
-        <is>
-          <t>29.4 - 29.4</t>
-        </is>
-      </c>
-      <c r="DT2" t="inlineStr">
-        <is>
-          <t>Milan</t>
-        </is>
-      </c>
-      <c r="DU2" t="n">
-        <v>425</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>3.2000008</v>
-      </c>
-      <c r="DW2" t="n">
-        <v>0.12678291</v>
-      </c>
-      <c r="DX2" t="inlineStr">
-        <is>
-          <t>25.24 - 49.0</t>
-        </is>
-      </c>
-      <c r="DY2" t="n">
-        <v>-20.56</v>
-      </c>
-      <c r="DZ2" t="n">
-        <v>-0.4195918</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>-31.682693</v>
-      </c>
-      <c r="EB2" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="EC2" t="n">
-        <v>0.070374586</v>
-      </c>
-      <c r="ED2" t="n">
-        <v>28.44</v>
       </c>
       <c r="EE2" t="inlineStr"/>
     </row>
